--- a/BUQUE_CLAUDE.xlsx
+++ b/BUQUE_CLAUDE.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="842">
   <si>
     <t>id_buque</t>
   </si>
@@ -1205,6 +1205,9 @@
     <t>MARIN0000000003</t>
   </si>
   <si>
+    <t>MARIN0000000004</t>
+  </si>
+  <si>
     <t>id_sanidad</t>
   </si>
   <si>
@@ -1277,6 +1280,9 @@
     <t>MER00005</t>
   </si>
   <si>
+    <t>Cajones de Botánica</t>
+  </si>
+  <si>
     <t>Cajón</t>
   </si>
   <si>
@@ -1298,6 +1304,9 @@
     <t>MER00006</t>
   </si>
   <si>
+    <t>Canela</t>
+  </si>
+  <si>
     <t>Real Hacienda de Filipinas</t>
   </si>
   <si>
@@ -1316,6 +1325,9 @@
     <t>MER00007</t>
   </si>
   <si>
+    <t>Cascarilla</t>
+  </si>
+  <si>
     <t>libras</t>
   </si>
   <si>
@@ -1373,27 +1385,33 @@
     <t>CARG000008</t>
   </si>
   <si>
-    <t>Cascarilla</t>
-  </si>
-  <si>
     <t>CARG000009</t>
   </si>
   <si>
     <t>MER00010</t>
   </si>
   <si>
+    <t>Semillas alfalfa</t>
+  </si>
+  <si>
     <t>CARG000010</t>
   </si>
   <si>
     <t>MER00011</t>
   </si>
   <si>
+    <t>Azúcar</t>
+  </si>
+  <si>
     <t>CARG000011</t>
   </si>
   <si>
     <t>MER00012</t>
   </si>
   <si>
+    <t>Chocolate</t>
+  </si>
+  <si>
     <t>CARG000012</t>
   </si>
   <si>
@@ -1472,12 +1490,18 @@
     <t>MER00021</t>
   </si>
   <si>
+    <t>Tabaco torcido</t>
+  </si>
+  <si>
     <t>CARG000021</t>
   </si>
   <si>
     <t>MER00022</t>
   </si>
   <si>
+    <t>Tabaco en polvo</t>
+  </si>
+  <si>
     <t>CARG000022</t>
   </si>
   <si>
@@ -1487,6 +1511,9 @@
     <t>MER00017</t>
   </si>
   <si>
+    <t>Miel blanca</t>
+  </si>
+  <si>
     <t>Botija</t>
   </si>
   <si>
@@ -1496,6 +1523,9 @@
     <t>MER00018</t>
   </si>
   <si>
+    <t>Miel de caña</t>
+  </si>
+  <si>
     <t>Barril</t>
   </si>
   <si>
@@ -1505,6 +1535,9 @@
     <t>MER00019</t>
   </si>
   <si>
+    <t>Cocos</t>
+  </si>
+  <si>
     <t>docena</t>
   </si>
   <si>
@@ -1514,12 +1547,18 @@
     <t>MER00020</t>
   </si>
   <si>
+    <t>Dulce</t>
+  </si>
+  <si>
     <t>CARG000027</t>
   </si>
   <si>
     <t>MER00023</t>
   </si>
   <si>
+    <t>Madera de cedro</t>
+  </si>
+  <si>
     <t>Pieza</t>
   </si>
   <si>
@@ -1529,12 +1568,18 @@
     <t>MER00024</t>
   </si>
   <si>
+    <t>Madera de caoba</t>
+  </si>
+  <si>
     <t>CARG000029</t>
   </si>
   <si>
     <t>MER00025</t>
   </si>
   <si>
+    <t>Pertrechos navales</t>
+  </si>
+  <si>
     <t>Departamento Marítimo de Ferrol</t>
   </si>
   <si>
@@ -1553,12 +1598,18 @@
     <t>MER00026</t>
   </si>
   <si>
+    <t>Cuerda mecha</t>
+  </si>
+  <si>
     <t>CARG000031</t>
   </si>
   <si>
     <t>MER00027</t>
   </si>
   <si>
+    <t>Víveres navales</t>
+  </si>
+  <si>
     <t>CARG000032</t>
   </si>
   <si>
@@ -1580,6 +1631,9 @@
     <t>MER00028</t>
   </si>
   <si>
+    <t>Pólvora</t>
+  </si>
+  <si>
     <t>CARG000035</t>
   </si>
   <si>
@@ -1595,31 +1649,22 @@
     <t>CARG000036</t>
   </si>
   <si>
+    <t>Real Hacienda de La Habana</t>
+  </si>
+  <si>
+    <t>JEF043</t>
+  </si>
+  <si>
     <t>CARG000037</t>
   </si>
   <si>
-    <t>Tabaco en polvo</t>
-  </si>
-  <si>
-    <t>Real Hacienda de La Habana</t>
-  </si>
-  <si>
-    <t>JEF043</t>
+    <t>MER00004</t>
+  </si>
+  <si>
+    <t>Azogue</t>
   </si>
   <si>
     <t>CARG000038</t>
-  </si>
-  <si>
-    <t>MER00004</t>
-  </si>
-  <si>
-    <t>Azogue</t>
-  </si>
-  <si>
-    <t>CARG000039</t>
-  </si>
-  <si>
-    <t>Pertrechos navales</t>
   </si>
   <si>
     <t>id_caudales</t>
@@ -2512,7 +2557,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -2571,10 +2616,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2604,7 +2645,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2661,6 +2702,7 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -2675,13 +2717,7 @@
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -4703,7 +4739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -4715,19 +4751,19 @@
         <v>280</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>8</v>
@@ -4735,7 +4771,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>134</v>
@@ -4747,24 +4783,24 @@
         <v>307</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>50</v>
@@ -4776,24 +4812,24 @@
         <v>307</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>743</v>
+        <v>758</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>159</v>
@@ -4805,21 +4841,21 @@
         <v>307</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>113</v>
@@ -4831,21 +4867,21 @@
         <v>307</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>46</v>
@@ -4857,21 +4893,21 @@
         <v>307</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>157</v>
@@ -4883,21 +4919,21 @@
         <v>307</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>162</v>
@@ -4909,21 +4945,21 @@
         <v>307</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>164</v>
@@ -4935,21 +4971,21 @@
         <v>307</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>749</v>
+        <v>764</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>166</v>
@@ -4961,21 +4997,21 @@
         <v>307</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>168</v>
@@ -4987,21 +5023,21 @@
         <v>307</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>170</v>
@@ -5013,21 +5049,21 @@
         <v>307</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>752</v>
+        <v>767</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>109</v>
@@ -5039,21 +5075,21 @@
         <v>307</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>753</v>
+        <v>768</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>64</v>
@@ -5065,21 +5101,21 @@
         <v>307</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>139</v>
@@ -5091,21 +5127,21 @@
         <v>307</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>142</v>
@@ -5117,21 +5153,21 @@
         <v>307</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>145</v>
@@ -5143,21 +5179,21 @@
         <v>307</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>757</v>
+        <v>772</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>147</v>
@@ -5169,21 +5205,21 @@
         <v>307</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>150</v>
@@ -5195,21 +5231,21 @@
         <v>307</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>759</v>
+        <v>774</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>153</v>
@@ -5221,21 +5257,21 @@
         <v>307</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>760</v>
+        <v>775</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>155</v>
@@ -5247,21 +5283,21 @@
         <v>307</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>172</v>
@@ -5273,21 +5309,21 @@
         <v>307</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>176</v>
@@ -5299,21 +5335,21 @@
         <v>307</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>179</v>
@@ -5325,21 +5361,21 @@
         <v>307</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>765</v>
+        <v>780</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>157</v>
@@ -5351,10 +5387,10 @@
         <v>312</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>313</v>
@@ -5365,7 +5401,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>111</v>
@@ -5377,7 +5413,7 @@
         <v>312</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>313</v>
@@ -5388,7 +5424,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>182</v>
@@ -5400,7 +5436,7 @@
         <v>312</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>313</v>
@@ -5411,7 +5447,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>134</v>
@@ -5423,24 +5459,24 @@
         <v>321</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>137</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>32</v>
@@ -5452,21 +5488,21 @@
         <v>321</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>168</v>
@@ -5478,21 +5514,21 @@
         <v>321</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>94</v>
@@ -5504,21 +5540,21 @@
         <v>321</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>182</v>
@@ -5530,18 +5566,18 @@
         <v>325</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>185</v>
@@ -5553,15 +5589,15 @@
         <v>325</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>187</v>
@@ -5570,13 +5606,13 @@
         <v>188</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>52</v>
@@ -5584,7 +5620,7 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>191</v>
@@ -5593,15 +5629,15 @@
         <v>192</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>193</v>
@@ -5610,15 +5646,15 @@
         <v>194</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>50</v>
@@ -5627,15 +5663,15 @@
         <v>51</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>195</v>
@@ -5644,15 +5680,15 @@
         <v>196</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>198</v>
@@ -5661,15 +5697,15 @@
         <v>199</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>12</v>
@@ -5678,15 +5714,15 @@
         <v>13</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>78</v>
@@ -5695,15 +5731,15 @@
         <v>79</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>26</v>
@@ -5712,15 +5748,15 @@
         <v>27</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>200</v>
@@ -5729,15 +5765,15 @@
         <v>201</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>202</v>
@@ -5746,15 +5782,15 @@
         <v>203</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>182</v>
@@ -5763,15 +5799,15 @@
         <v>183</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>204</v>
@@ -5780,15 +5816,15 @@
         <v>205</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>206</v>
@@ -5800,21 +5836,21 @@
         <v>307</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>209</v>
@@ -5826,21 +5862,21 @@
         <v>307</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>211</v>
@@ -5852,21 +5888,21 @@
         <v>307</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>797</v>
+        <v>812</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>214</v>
@@ -5878,21 +5914,21 @@
         <v>307</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>217</v>
@@ -5904,21 +5940,21 @@
         <v>307</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>231</v>
@@ -5930,21 +5966,21 @@
         <v>307</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>233</v>
@@ -5956,21 +5992,21 @@
         <v>307</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>235</v>
@@ -5982,21 +6018,21 @@
         <v>307</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>237</v>
@@ -6008,21 +6044,21 @@
         <v>307</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>239</v>
@@ -6034,21 +6070,21 @@
         <v>307</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>241</v>
@@ -6060,21 +6096,21 @@
         <v>307</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>243</v>
@@ -6086,21 +6122,21 @@
         <v>307</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>245</v>
@@ -6112,21 +6148,21 @@
         <v>307</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>247</v>
@@ -6138,21 +6174,21 @@
         <v>307</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>249</v>
@@ -6164,21 +6200,21 @@
         <v>307</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>809</v>
+        <v>824</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>251</v>
@@ -6190,21 +6226,21 @@
         <v>307</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>253</v>
@@ -6216,16 +6252,16 @@
         <v>307</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
   </sheetData>
@@ -6245,7 +6281,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -6257,15 +6293,15 @@
         <v>280</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>187</v>
@@ -6274,7 +6310,7 @@
         <v>188</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>54</v>
@@ -6285,7 +6321,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>191</v>
@@ -6294,7 +6330,7 @@
         <v>192</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>54</v>
@@ -6305,7 +6341,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>193</v>
@@ -6314,7 +6350,7 @@
         <v>194</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>54</v>
@@ -6325,7 +6361,7 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>50</v>
@@ -6334,7 +6370,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>54</v>
@@ -6345,7 +6381,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>195</v>
@@ -6354,7 +6390,7 @@
         <v>196</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>54</v>
@@ -6365,7 +6401,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>819</v>
+        <v>834</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>198</v>
@@ -6374,7 +6410,7 @@
         <v>199</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>54</v>
@@ -6385,7 +6421,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>12</v>
@@ -6394,7 +6430,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>54</v>
@@ -6405,7 +6441,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>821</v>
+        <v>836</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>78</v>
@@ -6414,7 +6450,7 @@
         <v>79</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>54</v>
@@ -6425,7 +6461,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>26</v>
@@ -6434,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>54</v>
@@ -6445,7 +6481,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>200</v>
@@ -6454,7 +6490,7 @@
         <v>201</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>54</v>
@@ -6465,7 +6501,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>202</v>
@@ -6474,7 +6510,7 @@
         <v>203</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>54</v>
@@ -6485,7 +6521,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>182</v>
@@ -6494,7 +6530,7 @@
         <v>183</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>54</v>
@@ -6505,7 +6541,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>204</v>
@@ -6514,7 +6550,7 @@
         <v>205</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>54</v>
@@ -7357,6 +7393,9 @@
       </c>
       <c r="I27" s="9" t="s">
         <v>379</v>
+      </c>
+      <c r="J27" s="4">
+        <v>8336.0</v>
       </c>
     </row>
   </sheetData>
@@ -7558,9 +7597,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="11"/>
+      <c r="A5" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="F5" s="18">
+        <v>116.0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>97.0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>155.0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>154.0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>25.0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>23.0</v>
+      </c>
+      <c r="N5" s="20">
+        <f>SUM(F5:M5)</f>
+        <v>610</v>
+      </c>
     </row>
     <row r="6">
       <c r="D6" s="11"/>
@@ -7588,8 +7665,8 @@
       <c r="F10" s="11"/>
     </row>
     <row r="11">
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="7"/>
     </row>
     <row r="12">
@@ -7633,8 +7710,8 @@
       <c r="F19" s="11"/>
     </row>
     <row r="20">
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="7"/>
     </row>
     <row r="21">
@@ -7701,7 +7778,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>279</v>
@@ -7713,25 +7790,25 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="J1" s="21"/>
+        <v>400</v>
+      </c>
+      <c r="J1" s="22"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>377</v>
@@ -7750,7 +7827,7 @@
         <v>20.0</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>290</v>
@@ -7768,7 +7845,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="5" max="6" width="9.25"/>
+    <col customWidth="1" min="2" max="2" width="9.75"/>
+    <col customWidth="1" min="3" max="3" width="10.38"/>
+    <col customWidth="1" min="4" max="4" width="10.63"/>
+    <col customWidth="1" min="5" max="5" width="15.63"/>
+    <col customWidth="1" min="6" max="6" width="9.25"/>
     <col customWidth="1" min="7" max="7" width="7.38"/>
     <col customWidth="1" min="8" max="8" width="9.13"/>
     <col customWidth="1" min="9" max="9" width="8.75"/>
@@ -7783,7 +7864,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>279</v>
@@ -7792,51 +7873,51 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="E1" s="22" t="s">
         <v>404</v>
       </c>
+      <c r="E1" s="23" t="s">
+        <v>405</v>
+      </c>
       <c r="F1" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="M1" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="M1" s="24" t="s">
         <v>412</v>
       </c>
+      <c r="N1" s="25" t="s">
+        <v>413</v>
+      </c>
       <c r="O1" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>298</v>
@@ -7845,39 +7926,41 @@
         <v>59</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="E2" s="4"/>
+        <v>418</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>419</v>
+      </c>
       <c r="F2" s="4">
         <v>5.0</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="26" t="s">
         <v>290</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>298</v>
@@ -7886,39 +7969,41 @@
         <v>59</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="E3" s="4"/>
+        <v>426</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>427</v>
+      </c>
       <c r="F3" s="4">
         <v>1.0</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="26" t="s">
         <v>290</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>301</v>
@@ -7927,39 +8012,45 @@
         <v>111</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="E4" s="4"/>
+        <v>433</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>434</v>
+      </c>
       <c r="F4" s="4">
         <v>80.0</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H4" s="4">
         <v>8124.0</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q4" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>301</v>
@@ -7968,34 +8059,40 @@
         <v>111</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="E5" s="4"/>
+        <v>418</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>419</v>
+      </c>
       <c r="F5" s="4">
         <v>2.0</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="27"/>
+        <v>437</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N5" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O5" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>301</v>
@@ -8004,41 +8101,45 @@
         <v>111</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>437</v>
+        <v>440</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>441</v>
       </c>
       <c r="F6" s="4">
         <v>1115.0</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="H6" s="4">
         <v>749.0</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N6" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O6" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>301</v>
@@ -8047,41 +8148,45 @@
         <v>111</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F7" s="4">
         <v>3376.0</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="H7" s="4">
         <v>6295.0</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M7" s="26"/>
-      <c r="N7" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N7" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O7" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>301</v>
@@ -8090,41 +8195,45 @@
         <v>111</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F8" s="4">
         <v>914.0</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="H8" s="4">
         <v>154666.0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M8" s="26"/>
-      <c r="N8" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N8" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O8" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>301</v>
@@ -8133,41 +8242,45 @@
         <v>111</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="F9" s="4">
         <v>144.0</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H9" s="4">
         <v>35203.0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M9" s="26"/>
-      <c r="N9" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N9" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O9" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>301</v>
@@ -8176,32 +8289,39 @@
         <v>111</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>452</v>
+        <v>455</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>456</v>
       </c>
       <c r="H10" s="4">
         <v>25.0</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M10" s="26"/>
-      <c r="N10" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N10" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O10" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>301</v>
@@ -8209,34 +8329,40 @@
       <c r="C11" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="E11" s="4"/>
+      <c r="D11" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>459</v>
+      </c>
       <c r="F11" s="4">
         <v>1.0</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M11" s="26"/>
-      <c r="N11" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N11" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O11" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>301</v>
@@ -8244,34 +8370,40 @@
       <c r="C12" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="E12" s="4"/>
+      <c r="D12" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>462</v>
+      </c>
       <c r="F12" s="4">
         <v>1.0</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M12" s="26"/>
-      <c r="N12" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="N12" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O12" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>341</v>
@@ -8280,39 +8412,39 @@
         <v>111</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="H13" s="4">
         <v>3231.0</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M13" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="M13" s="26" t="s">
         <v>331</v>
       </c>
-      <c r="N13" s="25" t="s">
+      <c r="N13" s="26" t="s">
         <v>290</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>341</v>
@@ -8321,39 +8453,39 @@
         <v>111</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="F14" s="4">
         <v>1.0</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M14" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="M14" s="26" t="s">
         <v>331</v>
       </c>
-      <c r="N14" s="25" t="s">
+      <c r="N14" s="26" t="s">
         <v>290</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>341</v>
@@ -8362,39 +8494,39 @@
         <v>111</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F15" s="4">
         <v>21.0</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M15" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="M15" s="26" t="s">
         <v>331</v>
       </c>
-      <c r="N15" s="25" t="s">
+      <c r="N15" s="26" t="s">
         <v>290</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>341</v>
@@ -8403,35 +8535,39 @@
         <v>111</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>468</v>
+        <v>473</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>474</v>
       </c>
       <c r="F16" s="4">
         <v>14.0</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M16" s="26"/>
-      <c r="N16" s="27"/>
+        <v>465</v>
+      </c>
+      <c r="M16" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="N16" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O16" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>341</v>
@@ -8440,35 +8576,39 @@
         <v>111</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>470</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>471</v>
+        <v>476</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>477</v>
       </c>
       <c r="F17" s="4">
         <v>41.0</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M17" s="26"/>
-      <c r="N17" s="27"/>
+        <v>465</v>
+      </c>
+      <c r="M17" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="N17" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O17" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>341</v>
@@ -8477,35 +8617,39 @@
         <v>111</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>474</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>475</v>
+        <v>480</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>481</v>
       </c>
       <c r="F18" s="4">
         <v>25.0</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M18" s="26"/>
-      <c r="N18" s="27"/>
+        <v>465</v>
+      </c>
+      <c r="M18" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="N18" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O18" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>341</v>
@@ -8514,35 +8658,39 @@
         <v>111</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>436</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>437</v>
+        <v>440</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>441</v>
       </c>
       <c r="F19" s="4">
         <v>11.0</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M19" s="26"/>
-      <c r="N19" s="27"/>
+        <v>465</v>
+      </c>
+      <c r="M19" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="N19" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O19" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>341</v>
@@ -8551,35 +8699,39 @@
         <v>111</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>479</v>
+        <v>484</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>485</v>
       </c>
       <c r="F20" s="4">
         <v>14.0</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M20" s="26"/>
-      <c r="N20" s="27"/>
+        <v>465</v>
+      </c>
+      <c r="M20" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="N20" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O20" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>353</v>
@@ -8588,33 +8740,39 @@
         <v>87</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>482</v>
-      </c>
-      <c r="E21" s="4"/>
+        <v>488</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>489</v>
+      </c>
       <c r="F21" s="4">
         <v>21.0</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M21" s="26"/>
-      <c r="N21" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="N21" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O21" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>353</v>
@@ -8623,33 +8781,39 @@
         <v>87</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="E22" s="4"/>
+        <v>491</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>492</v>
+      </c>
       <c r="F22" s="4">
         <v>1.0</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M22" s="26"/>
-      <c r="N22" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="N22" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O22" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>353</v>
@@ -8658,33 +8822,39 @@
         <v>87</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="E23" s="4"/>
+        <v>458</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>459</v>
+      </c>
       <c r="F23" s="4">
         <v>176.0</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M23" s="26"/>
-      <c r="N23" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="N23" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O23" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>353</v>
@@ -8693,33 +8863,39 @@
         <v>87</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="E24" s="4"/>
+        <v>495</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>496</v>
+      </c>
       <c r="F24" s="4">
         <v>103.0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M24" s="26"/>
-      <c r="N24" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="N24" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O24" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>353</v>
@@ -8728,33 +8904,39 @@
         <v>87</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="E25" s="4"/>
+        <v>499</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>500</v>
+      </c>
       <c r="F25" s="4">
         <v>3.0</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M25" s="26"/>
-      <c r="N25" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="N25" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O25" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>353</v>
@@ -8763,33 +8945,39 @@
         <v>87</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>493</v>
-      </c>
-      <c r="E26" s="4"/>
+        <v>503</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>504</v>
+      </c>
       <c r="F26" s="4">
         <v>4.0</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M26" s="26"/>
-      <c r="N26" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="N26" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O26" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>353</v>
@@ -8798,33 +8986,39 @@
         <v>87</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="E27" s="4"/>
+        <v>507</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>508</v>
+      </c>
       <c r="F27" s="4">
         <v>4.0</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="M27" s="26"/>
-      <c r="N27" s="27"/>
+        <v>445</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="N27" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O27" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>353</v>
@@ -8833,33 +9027,39 @@
         <v>87</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>498</v>
-      </c>
-      <c r="E28" s="4"/>
+        <v>510</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>511</v>
+      </c>
       <c r="F28" s="4">
         <v>186.0</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M28" s="26"/>
-      <c r="N28" s="27"/>
+        <v>465</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="N28" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O28" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>353</v>
@@ -8868,33 +9068,39 @@
         <v>87</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="E29" s="4"/>
+        <v>514</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>515</v>
+      </c>
       <c r="F29" s="4">
         <v>1.0</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M29" s="26"/>
-      <c r="N29" s="27"/>
+        <v>465</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="N29" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O29" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>344</v>
@@ -8903,27 +9109,34 @@
         <v>87</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>503</v>
+        <v>517</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>518</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="K30" s="11"/>
       <c r="L30" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="M30" s="26"/>
-      <c r="N30" s="27"/>
+        <v>520</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="N30" s="15" t="s">
+        <v>336</v>
+      </c>
       <c r="O30" s="4" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>351</v>
@@ -8932,36 +9145,39 @@
         <v>87</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>509</v>
+        <v>524</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>525</v>
       </c>
       <c r="H31" s="4">
         <v>84.0</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M31" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="M31" s="26" t="s">
         <v>331</v>
       </c>
-      <c r="N31" s="25" t="s">
-        <v>290</v>
+      <c r="N31" s="15" t="s">
+        <v>336</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>351</v>
@@ -8970,37 +9186,39 @@
         <v>87</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="E32" s="4"/>
+        <v>527</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>528</v>
+      </c>
       <c r="F32" s="4">
         <v>138.0</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M32" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="N32" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="N32" s="25" t="s">
-        <v>290</v>
-      </c>
       <c r="O32" s="4" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>351</v>
@@ -9009,33 +9227,39 @@
         <v>87</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="E33" s="4"/>
+        <v>447</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>448</v>
+      </c>
       <c r="F33" s="4">
         <v>1387.0</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M33" s="26"/>
-      <c r="N33" s="27"/>
+        <v>465</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="N33" s="15" t="s">
+        <v>336</v>
+      </c>
       <c r="O33" s="4" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>356</v>
@@ -9044,26 +9268,33 @@
         <v>87</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>503</v>
+        <v>517</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>518</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
+        <v>533</v>
+      </c>
+      <c r="M34" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="N34" s="15" t="s">
+        <v>336</v>
+      </c>
       <c r="O34" s="4" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>361</v>
@@ -9072,32 +9303,39 @@
         <v>87</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>518</v>
+        <v>535</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>536</v>
       </c>
       <c r="H35" s="4">
         <v>89.0</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
+        <v>465</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="N35" s="15" t="s">
+        <v>336</v>
+      </c>
       <c r="O35" s="4" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>361</v>
@@ -9106,35 +9344,39 @@
         <v>87</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="F36" s="4">
         <v>1700.0</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
+        <v>465</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="N36" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O36" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>363</v>
@@ -9143,76 +9385,80 @@
         <v>87</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>521</v>
+        <v>492</v>
       </c>
       <c r="F37" s="4">
-        <v>1700.0</v>
+        <v>400.0</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>522</v>
+        <v>452</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
+        <v>542</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="N37" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="O37" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="F38" s="4">
-        <v>400.0</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>448</v>
+        <v>545</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="H38" s="4">
+        <v>4000.0</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>443</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>527</v>
-      </c>
-      <c r="M38" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="N38" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="M38" s="26" t="s">
         <v>290</v>
       </c>
+      <c r="N38" s="15" t="s">
+        <v>331</v>
+      </c>
       <c r="O38" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q38" s="4" t="s">
-        <v>428</v>
+        <v>464</v>
+      </c>
+      <c r="Q38" s="11" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>365</v>
@@ -9220,77 +9466,36 @@
       <c r="C39" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>529</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>530</v>
-      </c>
-      <c r="H39" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>439</v>
+      <c r="D39" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>518</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="M39" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="M39" s="26" t="s">
         <v>290</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="Q39" s="11" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>503</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>532</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="M40" s="25" t="s">
-        <v>290</v>
-      </c>
-      <c r="N40" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="O40" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q40" s="4" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="11"/>
+        <v>521</v>
+      </c>
+      <c r="Q39" s="4" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -9313,7 +9518,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>279</v>
@@ -9322,39 +9527,39 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="I1" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="I1" s="25" t="s">
         <v>412</v>
       </c>
+      <c r="J1" s="25" t="s">
+        <v>413</v>
+      </c>
       <c r="K1" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>301</v>
@@ -9363,29 +9568,33 @@
         <v>111</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="E2" s="4">
         <v>2535946.0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="27"/>
+        <v>437</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K2" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>301</v>
@@ -9394,29 +9603,33 @@
         <v>111</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>539</v>
+        <v>554</v>
       </c>
       <c r="E3" s="4">
         <v>754748.0</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+        <v>437</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K3" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>301</v>
@@ -9425,29 +9638,33 @@
         <v>111</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="E4" s="4">
         <v>14000.0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+        <v>437</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K4" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>301</v>
@@ -9456,29 +9673,33 @@
         <v>111</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="E5" s="4">
         <v>59841.0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+        <v>437</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K5" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>301</v>
@@ -9487,29 +9708,33 @@
         <v>111</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="E6" s="4">
         <v>52118.0</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+        <v>437</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K6" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>301</v>
@@ -9518,29 +9743,33 @@
         <v>111</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="E7" s="4">
         <v>1669.0</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+        <v>437</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K7" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>301</v>
@@ -9549,29 +9778,33 @@
         <v>111</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="E8" s="4">
         <v>39754.0</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+        <v>437</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="J8" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K8" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>301</v>
@@ -9580,29 +9813,33 @@
         <v>111</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="E9" s="4">
         <v>108.0</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+        <v>437</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K9" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>341</v>
@@ -9611,29 +9848,33 @@
         <v>111</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="E10" s="4">
         <v>2338809.0</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+        <v>465</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K10" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>341</v>
@@ -9642,29 +9883,33 @@
         <v>111</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="E11" s="4">
         <v>1268829.0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+        <v>465</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K11" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>341</v>
@@ -9673,29 +9918,33 @@
         <v>111</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="E12" s="4">
         <v>98049.0</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>441</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
+        <v>445</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K12" s="11" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>341</v>
@@ -9704,29 +9953,33 @@
         <v>111</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="E13" s="4">
         <v>2000.0</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>441</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
+        <v>445</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K13" s="11" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>353</v>
@@ -9735,24 +9988,28 @@
         <v>87</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="E14" s="4">
         <v>10513.0</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>441</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
+        <v>445</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>290</v>
+      </c>
       <c r="K14" s="11" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15">
@@ -9783,31 +10040,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>562</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>563</v>
+        <v>576</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>578</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>279</v>
@@ -9815,31 +10072,31 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="28" t="s">
-        <v>569</v>
-      </c>
-      <c r="F2" s="25" t="s">
+      <c r="E2" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="26" t="s">
         <v>293</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>288</v>
@@ -9847,31 +10104,31 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>576</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="G3" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>591</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>290</v>
       </c>
+      <c r="G3" s="15" t="s">
+        <v>293</v>
+      </c>
       <c r="H3" s="4" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>288</v>
@@ -9879,19 +10136,19 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>293</v>
@@ -9900,7 +10157,7 @@
         <v>290</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>298</v>
@@ -9908,19 +10165,19 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>293</v>
@@ -9929,7 +10186,7 @@
         <v>290</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>298</v>
@@ -9937,31 +10194,31 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="28" t="s">
-        <v>569</v>
-      </c>
-      <c r="F6" s="25" t="s">
+      <c r="E6" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="F6" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="26" t="s">
         <v>293</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>295</v>
@@ -9969,31 +10226,31 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>597</v>
-      </c>
-      <c r="F7" s="15" t="s">
+        <v>612</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G7" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>288</v>
@@ -10001,31 +10258,31 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>600</v>
+        <v>615</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>602</v>
+        <v>617</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>603</v>
-      </c>
-      <c r="F8" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G8" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H8" s="4" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>288</v>
@@ -10033,28 +10290,28 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="F9" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G9" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H9" s="4" t="s">
-        <v>610</v>
+        <v>625</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>288</v>
@@ -10062,28 +10319,28 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>611</v>
+        <v>626</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>612</v>
+        <v>627</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>582</v>
+        <v>628</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>597</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>614</v>
-      </c>
-      <c r="F10" s="15" t="s">
+        <v>629</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G10" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>615</v>
+        <v>630</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>288</v>
@@ -10091,28 +10348,28 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>617</v>
+        <v>632</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>618</v>
+        <v>633</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="F11" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G11" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>620</v>
+        <v>635</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>288</v>
@@ -10120,28 +10377,28 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>622</v>
+        <v>637</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="F12" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G12" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>620</v>
+        <v>635</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>288</v>
@@ -10149,28 +10406,28 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>626</v>
+        <v>641</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="F13" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G13" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>620</v>
+        <v>635</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>288</v>
@@ -10178,31 +10435,31 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>627</v>
+        <v>642</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>628</v>
+        <v>643</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>629</v>
+        <v>644</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>630</v>
+        <v>645</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="F14" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G14" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H14" s="4" t="s">
-        <v>632</v>
+        <v>647</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>633</v>
+        <v>648</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>288</v>
@@ -10210,31 +10467,31 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>634</v>
+        <v>649</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>635</v>
+        <v>650</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>636</v>
+        <v>651</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>630</v>
+        <v>645</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="F15" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G15" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H15" s="4" t="s">
-        <v>632</v>
+        <v>647</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>633</v>
+        <v>648</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>288</v>
@@ -10242,28 +10499,28 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>641</v>
-      </c>
-      <c r="F16" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G16" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H16" s="11" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>288</v>
@@ -10271,28 +10528,28 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>646</v>
-      </c>
-      <c r="F17" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G17" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H17" s="11" t="s">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>288</v>
@@ -10300,28 +10557,28 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>646</v>
-      </c>
-      <c r="F18" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G18" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>290</v>
-      </c>
       <c r="H18" s="11" t="s">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>288</v>
@@ -10329,25 +10586,25 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F19" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G19" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>389</v>
@@ -10358,25 +10615,25 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>656</v>
+        <v>671</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F20" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G20" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>389</v>
@@ -10387,25 +10644,25 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>661</v>
+        <v>676</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F21" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G21" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>389</v>
@@ -10416,25 +10673,25 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>663</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>664</v>
+        <v>678</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>679</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F22" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G22" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>389</v>
@@ -10445,25 +10702,25 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>665</v>
+        <v>680</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>666</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>667</v>
+        <v>681</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>682</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F23" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G23" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>389</v>
@@ -10474,25 +10731,25 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>668</v>
+        <v>683</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>684</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="E24" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G24" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>389</v>
@@ -10503,25 +10760,25 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>671</v>
+        <v>686</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>672</v>
+        <v>687</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>673</v>
+        <v>688</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F25" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G25" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>389</v>
@@ -10532,25 +10789,25 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>676</v>
+        <v>691</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F26" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G26" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>389</v>
@@ -10561,25 +10818,25 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>677</v>
+        <v>692</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>678</v>
+        <v>693</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>679</v>
+        <v>694</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F27" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G27" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>389</v>
@@ -10590,25 +10847,25 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>681</v>
+        <v>696</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>682</v>
+        <v>697</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F28" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G28" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>389</v>
@@ -10619,25 +10876,25 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>683</v>
+        <v>698</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F29" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G29" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>389</v>
@@ -10648,25 +10905,25 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>686</v>
+        <v>701</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>687</v>
+        <v>702</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F30" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G30" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>389</v>
@@ -10677,25 +10934,25 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>690</v>
+        <v>705</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>691</v>
+        <v>706</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>655</v>
-      </c>
-      <c r="F31" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G31" s="26" t="s">
         <v>293</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>389</v>
@@ -10706,19 +10963,19 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>692</v>
+        <v>707</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>693</v>
+        <v>708</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>694</v>
+        <v>709</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>695</v>
-      </c>
-      <c r="E32" s="28" t="s">
-        <v>696</v>
+        <v>710</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>711</v>
       </c>
       <c r="F32" s="15" t="s">
         <v>331</v>
@@ -10727,7 +10984,7 @@
         <v>290</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>697</v>
+        <v>712</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>341</v>
@@ -10735,19 +10992,19 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>698</v>
+        <v>713</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>699</v>
+        <v>714</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="28" t="s">
-        <v>609</v>
+      <c r="E33" s="20" t="s">
+        <v>624</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>290</v>
@@ -10756,7 +11013,7 @@
         <v>336</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>610</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -10785,7 +11042,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>701</v>
+        <v>716</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -10797,31 +11054,31 @@
         <v>280</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>702</v>
+        <v>717</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>562</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>563</v>
+        <v>718</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>578</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>705</v>
+        <v>720</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>706</v>
+        <v>721</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>707</v>
+        <v>722</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>279</v>
@@ -10829,7 +11086,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>179</v>
@@ -10841,17 +11098,17 @@
         <v>307</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="G2" s="25" t="s">
+        <v>726</v>
+      </c>
+      <c r="G2" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="H2" s="30"/>
+      <c r="H2" s="29"/>
       <c r="I2" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="J2" s="4">
         <v>7.0</v>
@@ -10871,7 +11128,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>172</v>
@@ -10883,15 +11140,15 @@
         <v>307</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="J3" s="4">
         <v>7.0</v>
@@ -10911,7 +11168,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>211</v>
@@ -10923,15 +11180,15 @@
         <v>307</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="J4" s="4">
         <v>7.0</v>
@@ -10951,7 +11208,7 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>217</v>
@@ -10963,15 +11220,15 @@
         <v>307</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="J5" s="4">
         <v>5.0</v>
@@ -10991,7 +11248,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>87</v>
@@ -11000,10 +11257,10 @@
         <v>88</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>346</v>
@@ -11017,7 +11274,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>87</v>
@@ -11026,10 +11283,10 @@
         <v>88</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="G7" s="15" t="s">
         <v>346</v>
@@ -11043,7 +11300,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>74</v>
@@ -11052,10 +11309,16 @@
         <v>75</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>724</v>
+        <v>739</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>336</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>365</v>
@@ -11063,7 +11326,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>74</v>
@@ -11072,10 +11335,16 @@
         <v>75</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>727</v>
+        <v>742</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>336</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>365</v>
